--- a/public/plantillagrupo.xlsx
+++ b/public/plantillagrupo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wamp64\www\cargaHorariav2\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9AF2B4-0268-4CC8-97ED-C6B673ADA052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585C0770-1B29-4082-B209-4F4C116E3864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>Horas totales:</t>
-  </si>
-  <si>
-    <t>Horas frente a grupo:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>HORA</t>
   </si>
@@ -93,38 +87,20 @@
     <t>19:00 - 20:00</t>
   </si>
   <si>
-    <t>SUBDIRECTORA DE CARRERA</t>
+    <t>HORARIO CUATRIMESTRAL SEPTIEMBRE - DICIEMBRE 2025</t>
   </si>
   <si>
-    <t>DIRECTOR ACADÉMICO</t>
+    <t>Grupo:</t>
   </si>
   <si>
-    <t>SELLO PLANEACIÓN Y EVALUACIÓN</t>
-  </si>
-  <si>
-    <t>FIRMA DE CONOCIMIENTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELLO DELEGACIÓN ADMINISTRATIVA                                         </t>
-  </si>
-  <si>
-    <t>COMISIÓN ACADÉMICA DICTAMINADORA</t>
-  </si>
-  <si>
-    <t>DOCENTE</t>
-  </si>
-  <si>
-    <t>Nombre del Grupo:</t>
-  </si>
-  <si>
-    <t>HORARIO CUATRIMESTRAL SEPTIEMBRE - DICIEMBRE 2025</t>
+    <t>Nombre del Programa:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -151,29 +127,9 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
@@ -181,33 +137,6 @@
       <sz val="20"/>
       <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -237,7 +166,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -249,48 +178,9 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -321,17 +211,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -348,103 +227,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -520,68 +302,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -662,182 +382,109 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1220,13 +867,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55"/>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
+      <c r="A1" s="15"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -1248,15 +895,15 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="51" t="s">
-        <v>30</v>
+      <c r="A2" s="11" t="s">
+        <v>20</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="58"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -1278,17 +925,17 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
-        <v>29</v>
+      <c r="A3" s="11" t="s">
+        <v>22</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="6" t="s">
-        <v>0</v>
+      <c r="B3" s="12"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="24" t="s">
+        <v>21</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="26"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
@@ -1310,15 +957,13 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="53"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="25"/>
+      <c r="G4" s="27"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -1340,26 +985,26 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>8</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1382,15 +1027,15 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>9</v>
+      <c r="A6" s="8" t="s">
+        <v>7</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="13"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
@@ -1412,15 +1057,15 @@
       <c r="Z6" s="1"/>
     </row>
     <row r="7" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>10</v>
+      <c r="A7" s="8" t="s">
+        <v>8</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="13"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1442,15 +1087,15 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>11</v>
+      <c r="A8" s="8" t="s">
+        <v>9</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
@@ -1472,15 +1117,15 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>12</v>
+      <c r="A9" s="8" t="s">
+        <v>10</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="13"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
@@ -1502,15 +1147,15 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>13</v>
+      <c r="A10" s="8" t="s">
+        <v>11</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="13"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="10"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
@@ -1532,15 +1177,15 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>14</v>
+      <c r="A11" s="8" t="s">
+        <v>12</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="13"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="10"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
@@ -1562,15 +1207,15 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>15</v>
+      <c r="A12" s="8" t="s">
+        <v>13</v>
       </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="10"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
@@ -1592,15 +1237,15 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>16</v>
+      <c r="A13" s="8" t="s">
+        <v>14</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="10"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
@@ -1622,15 +1267,15 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>17</v>
+      <c r="A14" s="8" t="s">
+        <v>15</v>
       </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="13"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="10"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
@@ -1652,15 +1297,15 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>18</v>
+      <c r="A15" s="8" t="s">
+        <v>16</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="13"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1682,15 +1327,15 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>19</v>
+      <c r="A16" s="8" t="s">
+        <v>17</v>
       </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="13"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
@@ -1712,15 +1357,15 @@
       <c r="Z16" s="1"/>
     </row>
     <row r="17" spans="1:26" ht="109.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>20</v>
+      <c r="A17" s="8" t="s">
+        <v>18</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="13"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
@@ -1742,15 +1387,15 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>21</v>
+      <c r="A18" s="8" t="s">
+        <v>19</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="13"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
@@ -1771,14 +1416,14 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="59"/>
-      <c r="B19" s="59"/>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
+    <row r="19" spans="1:26" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
@@ -1791,56 +1436,29 @@
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-    </row>
-    <row r="20" spans="1:26" ht="121.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="39"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="29"/>
+    </row>
+    <row r="20" spans="1:26" ht="121.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="48"/>
-      <c r="C21" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="15"/>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -1853,22 +1471,15 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-    </row>
-    <row r="22" spans="1:26" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="49"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="19"/>
+    </row>
+    <row r="22" spans="1:26" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -1881,24 +1492,15 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-    </row>
-    <row r="23" spans="1:26" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="30"/>
+    </row>
+    <row r="23" spans="1:26" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -1911,22 +1513,15 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-    </row>
-    <row r="24" spans="1:26" ht="103.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="41"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="35"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
+    </row>
+    <row r="24" spans="1:26" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
@@ -1939,26 +1534,15 @@
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="21"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
       <c r="J25" s="1"/>
@@ -1971,22 +1555,15 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
     </row>
     <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
       <c r="J26" s="1"/>
@@ -1999,24 +1576,15 @@
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
-    </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
+    </row>
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1"/>
@@ -2029,22 +1597,15 @@
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
     </row>
     <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="26"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="23"/>
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
@@ -2057,22 +1618,15 @@
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-    </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="37"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="25"/>
+    </row>
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
@@ -2085,13 +1639,6 @@
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
     </row>
     <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
@@ -8442,29 +7989,13 @@
     <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="F21:G22"/>
+  <mergeCells count="6">
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
     <mergeCell ref="C3:E4"/>
-    <mergeCell ref="C25:E29"/>
-    <mergeCell ref="F25:G29"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.22326454033771001" right="0.22326454033771001" top="0.20731707317073" bottom="0.22326454033771001" header="0" footer="0"/>
